--- a/Result/profitability/1303.xlsx
+++ b/Result/profitability/1303.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.07</v>
       </c>
       <c r="M2" t="n">
-        <v>0.43625</v>
+        <v>0.85625</v>
       </c>
       <c r="N2" t="n">
-        <v>9.703749999999999</v>
+        <v>11.03125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.61</v>
+        <v>1.02625</v>
       </c>
       <c r="N3" t="n">
-        <v>10.52</v>
+        <v>12.05875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>0.78</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7025</v>
+        <v>1.11625</v>
       </c>
       <c r="N4" t="n">
-        <v>10.95875</v>
+        <v>12.4425</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4425</v>
+        <v>0.9287499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9.9925</v>
+        <v>11.2775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.46</v>
       </c>
       <c r="M6" t="n">
-        <v>0.45</v>
+        <v>0.82</v>
       </c>
       <c r="N6" t="n">
-        <v>9.119999999999999</v>
+        <v>10.44875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.71</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4874999999999999</v>
+        <v>0.8312499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>9.75375</v>
+        <v>10.9625</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.87</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5187499999999999</v>
+        <v>0.715</v>
       </c>
       <c r="N8" t="n">
-        <v>10.2475</v>
+        <v>11.12</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>83647</v>
+      </c>
+      <c r="D75" t="n">
+        <v>67822</v>
+      </c>
+      <c r="E75" t="n">
+        <v>15825</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="G75" t="n">
+        <v>11357</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.58%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>19407</v>
+      </c>
+      <c r="J75" t="n">
+        <v>30764</v>
+      </c>
+      <c r="K75" t="n">
+        <v>26753</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.7237499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8722222222222222</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>6.980000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.5845896147403686</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-7.480769230769231</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.189814814814815</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
